--- a/tame_output/MOZAIC/bt/btc_vs_alt_20230725.xlsx
+++ b/tame_output/MOZAIC/bt/btc_vs_alt_20230725.xlsx
@@ -45254,10 +45254,10 @@
         <v>1.275216243944096</v>
       </c>
       <c r="D1724" t="n">
-        <v>1.116858930478812</v>
+        <v>1.116858930478813</v>
       </c>
       <c r="E1724" t="n">
-        <v>1.196037587211454</v>
+        <v>1.196037587211455</v>
       </c>
       <c r="F1724" t="n">
         <v>4.091157023518958</v>
@@ -45306,7 +45306,7 @@
         <v>1.243951891303042</v>
       </c>
       <c r="D1726" t="n">
-        <v>1.09310559804205</v>
+        <v>1.093105598042051</v>
       </c>
       <c r="E1726" t="n">
         <v>1.168528744672546</v>
@@ -45332,7 +45332,7 @@
         <v>1.243585736499002</v>
       </c>
       <c r="D1727" t="n">
-        <v>1.094874190796777</v>
+        <v>1.094874190796778</v>
       </c>
       <c r="E1727" t="n">
         <v>1.16922996364789</v>
@@ -45358,7 +45358,7 @@
         <v>1.237422814169738</v>
       </c>
       <c r="D1728" t="n">
-        <v>1.088762329359653</v>
+        <v>1.088762329359654</v>
       </c>
       <c r="E1728" t="n">
         <v>1.163092571764696</v>
@@ -45384,7 +45384,7 @@
         <v>1.213894068863914</v>
       </c>
       <c r="D1729" t="n">
-        <v>1.076173148844249</v>
+        <v>1.07617314884425</v>
       </c>
       <c r="E1729" t="n">
         <v>1.145033608854082</v>
@@ -45410,7 +45410,7 @@
         <v>1.207213571245792</v>
       </c>
       <c r="D1730" t="n">
-        <v>1.066555024024783</v>
+        <v>1.066555024024784</v>
       </c>
       <c r="E1730" t="n">
         <v>1.136884297635288</v>
@@ -45439,7 +45439,7 @@
         <v>1.069914605703315</v>
       </c>
       <c r="E1731" t="n">
-        <v>1.139730580924037</v>
+        <v>1.139730580924038</v>
       </c>
       <c r="F1731" t="n">
         <v>4.154262707986497</v>
@@ -45462,7 +45462,7 @@
         <v>1.224973792954506</v>
       </c>
       <c r="D1732" t="n">
-        <v>1.083376225070938</v>
+        <v>1.083376225070939</v>
       </c>
       <c r="E1732" t="n">
         <v>1.154175009012722</v>
@@ -45488,7 +45488,7 @@
         <v>1.23013067580833</v>
       </c>
       <c r="D1733" t="n">
-        <v>1.081039731397426</v>
+        <v>1.081039731397427</v>
       </c>
       <c r="E1733" t="n">
         <v>1.155585203602878</v>
@@ -45514,7 +45514,7 @@
         <v>1.23817153480487</v>
       </c>
       <c r="D1734" t="n">
-        <v>1.093508654338623</v>
+        <v>1.093508654338624</v>
       </c>
       <c r="E1734" t="n">
         <v>1.165840094571747</v>
@@ -45543,7 +45543,7 @@
         <v>1.093045682616289</v>
       </c>
       <c r="E1735" t="n">
-        <v>1.164657724993408</v>
+        <v>1.164657724993409</v>
       </c>
       <c r="F1735" t="n">
         <v>4.169008396137246</v>
@@ -45566,7 +45566,7 @@
         <v>1.23043717370799</v>
       </c>
       <c r="D1736" t="n">
-        <v>1.088425401503023</v>
+        <v>1.088425401503024</v>
       </c>
       <c r="E1736" t="n">
         <v>1.159431287605507</v>
@@ -45592,10 +45592,10 @@
         <v>1.237664140934303</v>
       </c>
       <c r="D1737" t="n">
-        <v>1.093258702567099</v>
+        <v>1.0932587025671</v>
       </c>
       <c r="E1737" t="n">
-        <v>1.165461421750701</v>
+        <v>1.165461421750702</v>
       </c>
       <c r="F1737" t="n">
         <v>4.173316649937499</v>
@@ -45618,7 +45618,7 @@
         <v>1.240375862993066</v>
       </c>
       <c r="D1738" t="n">
-        <v>1.095484819578506</v>
+        <v>1.095484819578507</v>
       </c>
       <c r="E1738" t="n">
         <v>1.167930341285786</v>
@@ -45670,7 +45670,7 @@
         <v>1.246943518396535</v>
       </c>
       <c r="D1740" t="n">
-        <v>1.110382060946549</v>
+        <v>1.11038206094655</v>
       </c>
       <c r="E1740" t="n">
         <v>1.178662789671542</v>
@@ -45774,7 +45774,7 @@
         <v>1.236289953641316</v>
       </c>
       <c r="D1744" t="n">
-        <v>1.09369336727536</v>
+        <v>1.093693367275361</v>
       </c>
       <c r="E1744" t="n">
         <v>1.164991660458338</v>
@@ -45826,7 +45826,7 @@
         <v>1.241975089358957</v>
       </c>
       <c r="D1746" t="n">
-        <v>1.096209076509433</v>
+        <v>1.096209076509434</v>
       </c>
       <c r="E1746" t="n">
         <v>1.169092082934195</v>
@@ -45956,7 +45956,7 @@
         <v>1.275010296455434</v>
       </c>
       <c r="D1751" t="n">
-        <v>1.117892265621632</v>
+        <v>1.117892265621633</v>
       </c>
       <c r="E1751" t="n">
         <v>1.196451281038533</v>
@@ -45968,7 +45968,7 @@
         <v>4.169945989801893</v>
       </c>
       <c r="H1751" t="n">
-        <v>4.201369595968638</v>
+        <v>4.201369595968639</v>
       </c>
     </row>
     <row r="1752">
@@ -45982,10 +45982,10 @@
         <v>1.277421339303118</v>
       </c>
       <c r="D1752" t="n">
-        <v>1.115862956504818</v>
+        <v>1.115862956504819</v>
       </c>
       <c r="E1752" t="n">
-        <v>1.196642147903968</v>
+        <v>1.196642147903969</v>
       </c>
       <c r="F1752" t="n">
         <v>4.243177513610931</v>
@@ -45994,7 +45994,7 @@
         <v>4.17855416049162</v>
       </c>
       <c r="H1752" t="n">
-        <v>4.210865837051264</v>
+        <v>4.210865837051265</v>
       </c>
     </row>
     <row r="1753">
@@ -46020,7 +46020,7 @@
         <v>4.199406520077472</v>
       </c>
       <c r="H1753" t="n">
-        <v>4.232179528843632</v>
+        <v>4.232179528843633</v>
       </c>
     </row>
     <row r="1754">
@@ -46046,7 +46046,7 @@
         <v>4.173767193339407</v>
       </c>
       <c r="H1754" t="n">
-        <v>4.206913206340589</v>
+        <v>4.20691320634059</v>
       </c>
     </row>
     <row r="1755">
@@ -46072,7 +46072,7 @@
         <v>4.161767436103266</v>
       </c>
       <c r="H1755" t="n">
-        <v>4.194329688117936</v>
+        <v>4.194329688117937</v>
       </c>
     </row>
     <row r="1756">
@@ -46098,7 +46098,7 @@
         <v>4.136157813001615</v>
       </c>
       <c r="H1756" t="n">
-        <v>4.168415399722076</v>
+        <v>4.168415399722077</v>
       </c>
     </row>
     <row r="1757">
@@ -46124,7 +46124,7 @@
         <v>4.159763288066026</v>
       </c>
       <c r="H1757" t="n">
-        <v>4.192267517392497</v>
+        <v>4.192267517392498</v>
       </c>
     </row>
     <row r="1758">
@@ -46176,7 +46176,7 @@
         <v>4.158258180307532</v>
       </c>
       <c r="H1759" t="n">
-        <v>4.191153978350577</v>
+        <v>4.191153978350578</v>
       </c>
     </row>
     <row r="1760">
@@ -46202,7 +46202,7 @@
         <v>4.156040816485986</v>
       </c>
       <c r="H1760" t="n">
-        <v>4.186919376259058</v>
+        <v>4.186919376259059</v>
       </c>
     </row>
     <row r="1761">
@@ -46228,7 +46228,7 @@
         <v>4.156311088915389</v>
       </c>
       <c r="H1761" t="n">
-        <v>4.185020482806953</v>
+        <v>4.185020482806954</v>
       </c>
     </row>
     <row r="1762">
@@ -46254,7 +46254,7 @@
         <v>4.184437999499486</v>
       </c>
       <c r="H1762" t="n">
-        <v>4.210915214480423</v>
+        <v>4.210915214480424</v>
       </c>
     </row>
     <row r="1763">
@@ -46306,7 +46306,7 @@
         <v>4.169101096816423</v>
       </c>
       <c r="H1764" t="n">
-        <v>4.196649391061089</v>
+        <v>4.19664939106109</v>
       </c>
     </row>
     <row r="1765">
@@ -46332,7 +46332,7 @@
         <v>4.280504956762069</v>
       </c>
       <c r="H1765" t="n">
-        <v>4.303806727983336</v>
+        <v>4.303806727983337</v>
       </c>
     </row>
     <row r="1766">
@@ -46358,7 +46358,7 @@
         <v>4.263312251898633</v>
       </c>
       <c r="H1766" t="n">
-        <v>4.288218586212472</v>
+        <v>4.288218586212473</v>
       </c>
     </row>
     <row r="1767">
@@ -46384,7 +46384,7 @@
         <v>4.270718215337832</v>
       </c>
       <c r="H1767" t="n">
-        <v>4.29643630490587</v>
+        <v>4.296436304905871</v>
       </c>
     </row>
     <row r="1768">
@@ -46436,7 +46436,7 @@
         <v>4.260659035410258</v>
       </c>
       <c r="H1769" t="n">
-        <v>4.288216059091863</v>
+        <v>4.288216059091864</v>
       </c>
     </row>
     <row r="1770">
@@ -46462,7 +46462,7 @@
         <v>4.249383573804507</v>
       </c>
       <c r="H1770" t="n">
-        <v>4.278843596315763</v>
+        <v>4.278843596315764</v>
       </c>
     </row>
     <row r="1771">
@@ -46488,7 +46488,7 @@
         <v>4.279774332325052</v>
       </c>
       <c r="H1771" t="n">
-        <v>4.305607534206382</v>
+        <v>4.305607534206383</v>
       </c>
     </row>
     <row r="1772">
@@ -46514,7 +46514,7 @@
         <v>4.295264224359174</v>
       </c>
       <c r="H1772" t="n">
-        <v>4.321875894966054</v>
+        <v>4.321875894966055</v>
       </c>
     </row>
     <row r="1773">
@@ -46540,7 +46540,7 @@
         <v>4.280355958484511</v>
       </c>
       <c r="H1773" t="n">
-        <v>4.307374800106707</v>
+        <v>4.307374800106708</v>
       </c>
     </row>
     <row r="1774">
@@ -46566,7 +46566,7 @@
         <v>4.300392045139563</v>
       </c>
       <c r="H1774" t="n">
-        <v>4.328803662441677</v>
+        <v>4.328803662441678</v>
       </c>
     </row>
     <row r="1775">
@@ -46592,7 +46592,7 @@
         <v>4.273206718339313</v>
       </c>
       <c r="H1775" t="n">
-        <v>4.302858340724391</v>
+        <v>4.302858340724393</v>
       </c>
     </row>
     <row r="1776">
@@ -46618,7 +46618,7 @@
         <v>4.200009134708798</v>
       </c>
       <c r="H1776" t="n">
-        <v>4.233080150660806</v>
+        <v>4.233080150660808</v>
       </c>
     </row>
     <row r="1777">
@@ -46644,7 +46644,7 @@
         <v>4.274223733566947</v>
       </c>
       <c r="H1777" t="n">
-        <v>4.305756017145073</v>
+        <v>4.305756017145074</v>
       </c>
     </row>
     <row r="1778">
@@ -46670,7 +46670,7 @@
         <v>4.266396923479366</v>
       </c>
       <c r="H1778" t="n">
-        <v>4.297030507558532</v>
+        <v>4.297030507558533</v>
       </c>
     </row>
     <row r="1779">
@@ -46696,7 +46696,7 @@
         <v>4.253204775732452</v>
       </c>
       <c r="H1779" t="n">
-        <v>4.283838359811617</v>
+        <v>4.283838359811619</v>
       </c>
     </row>
     <row r="1780">
@@ -46722,7 +46722,7 @@
         <v>4.248395397879476</v>
       </c>
       <c r="H1780" t="n">
-        <v>4.279065302533986</v>
+        <v>4.279065302533987</v>
       </c>
     </row>
     <row r="1781">
@@ -46748,7 +46748,7 @@
         <v>4.24492458738736</v>
       </c>
       <c r="H1781" t="n">
-        <v>4.275359250170402</v>
+        <v>4.275359250170403</v>
       </c>
     </row>
     <row r="1782">
@@ -46774,7 +46774,7 @@
         <v>4.246698020972403</v>
       </c>
       <c r="H1782" t="n">
-        <v>4.277270481803771</v>
+        <v>4.277270481803773</v>
       </c>
     </row>
     <row r="1783">
@@ -46800,7 +46800,7 @@
         <v>4.242787704254172</v>
       </c>
       <c r="H1783" t="n">
-        <v>4.273661063992945</v>
+        <v>4.273661063992947</v>
       </c>
     </row>
     <row r="1784">
@@ -46826,7 +46826,7 @@
         <v>4.255067871088617</v>
       </c>
       <c r="H1784" t="n">
-        <v>4.287444734269737</v>
+        <v>4.287444734269739</v>
       </c>
     </row>
     <row r="1785">
@@ -46852,7 +46852,7 @@
         <v>4.254201426763957</v>
       </c>
       <c r="H1785" t="n">
-        <v>4.286352184147139</v>
+        <v>4.286352184147141</v>
       </c>
     </row>
     <row r="1786">
@@ -46878,7 +46878,7 @@
         <v>4.259609118359341</v>
       </c>
       <c r="H1786" t="n">
-        <v>4.291439219510669</v>
+        <v>4.291439219510671</v>
       </c>
     </row>
     <row r="1787">
@@ -46904,7 +46904,7 @@
         <v>4.24234923456564</v>
       </c>
       <c r="H1787" t="n">
-        <v>4.274777721579882</v>
+        <v>4.274777721579884</v>
       </c>
     </row>
     <row r="1788">
@@ -46930,7 +46930,7 @@
         <v>4.231259011830753</v>
       </c>
       <c r="H1788" t="n">
-        <v>4.263540904646652</v>
+        <v>4.263540904646653</v>
       </c>
     </row>
     <row r="1789">
@@ -46956,7 +46956,7 @@
         <v>4.272781982798175</v>
       </c>
       <c r="H1789" t="n">
-        <v>4.30538785585486</v>
+        <v>4.305387855854861</v>
       </c>
     </row>
     <row r="1790">
@@ -46982,7 +46982,7 @@
         <v>4.294824486826659</v>
       </c>
       <c r="H1790" t="n">
-        <v>4.327918828611118</v>
+        <v>4.32791882861112</v>
       </c>
     </row>
     <row r="1791">
@@ -47008,7 +47008,7 @@
         <v>4.296071439979695</v>
       </c>
       <c r="H1791" t="n">
-        <v>4.32934344562999</v>
+        <v>4.329343445629991</v>
       </c>
     </row>
     <row r="1792">
@@ -47034,7 +47034,7 @@
         <v>4.288592923198624</v>
       </c>
       <c r="H1792" t="n">
-        <v>4.320794689355286</v>
+        <v>4.320794689355288</v>
       </c>
     </row>
     <row r="1793">
@@ -47060,7 +47060,7 @@
         <v>4.294663364757498</v>
       </c>
       <c r="H1793" t="n">
-        <v>4.326622905590526</v>
+        <v>4.326622905590527</v>
       </c>
     </row>
     <row r="1794">
@@ -47086,7 +47086,7 @@
         <v>4.293040687528048</v>
       </c>
       <c r="H1794" t="n">
-        <v>4.324324533199785</v>
+        <v>4.324324533199787</v>
       </c>
     </row>
     <row r="1795">
@@ -47112,7 +47112,7 @@
         <v>4.289607710769149</v>
       </c>
       <c r="H1795" t="n">
-        <v>4.320753034912931</v>
+        <v>4.320753034912933</v>
       </c>
     </row>
     <row r="1796">
@@ -47138,7 +47138,7 @@
         <v>4.297719053444676</v>
       </c>
       <c r="H1796" t="n">
-        <v>4.328471904493915</v>
+        <v>4.328471904493917</v>
       </c>
     </row>
     <row r="1797">
@@ -47164,7 +47164,7 @@
         <v>4.314365809558218</v>
       </c>
       <c r="H1797" t="n">
-        <v>4.3473014865238</v>
+        <v>4.347301486523802</v>
       </c>
     </row>
     <row r="1798">
@@ -47190,7 +47190,7 @@
         <v>4.302137553017811</v>
       </c>
       <c r="H1798" t="n">
-        <v>4.336054518278558</v>
+        <v>4.336054518278559</v>
       </c>
     </row>
     <row r="1799">
@@ -47216,7 +47216,7 @@
         <v>4.301234275415843</v>
       </c>
       <c r="H1799" t="n">
-        <v>4.335044146954995</v>
+        <v>4.335044146954997</v>
       </c>
     </row>
     <row r="1800">
@@ -47242,7 +47242,7 @@
         <v>4.289742939472696</v>
       </c>
       <c r="H1800" t="n">
-        <v>4.323667816646561</v>
+        <v>4.323667816646562</v>
       </c>
     </row>
     <row r="1801">
@@ -47268,7 +47268,7 @@
         <v>4.289669318546722</v>
       </c>
       <c r="H1801" t="n">
-        <v>4.324138475201454</v>
+        <v>4.324138475201456</v>
       </c>
     </row>
     <row r="1802">
@@ -47294,7 +47294,7 @@
         <v>4.288027512590445</v>
       </c>
       <c r="H1802" t="n">
-        <v>4.322071326469451</v>
+        <v>4.322071326469453</v>
       </c>
     </row>
     <row r="1803">
@@ -47320,7 +47320,7 @@
         <v>4.283579975315359</v>
       </c>
       <c r="H1803" t="n">
-        <v>4.318217686276371</v>
+        <v>4.318217686276373</v>
       </c>
     </row>
     <row r="1804">
@@ -47346,7 +47346,7 @@
         <v>4.274591747196093</v>
       </c>
       <c r="H1804" t="n">
-        <v>4.309432526516159</v>
+        <v>4.309432526516161</v>
       </c>
     </row>
     <row r="1805">
@@ -47372,7 +47372,7 @@
         <v>4.287151620429515</v>
       </c>
       <c r="H1805" t="n">
-        <v>4.321846331423822</v>
+        <v>4.321846331423824</v>
       </c>
     </row>
     <row r="1806">
@@ -47398,7 +47398,7 @@
         <v>4.284596272740203</v>
       </c>
       <c r="H1806" t="n">
-        <v>4.319744881026836</v>
+        <v>4.319744881026837</v>
       </c>
     </row>
     <row r="1807">
@@ -47424,7 +47424,7 @@
         <v>4.285305334669818</v>
       </c>
       <c r="H1807" t="n">
-        <v>4.320532705448144</v>
+        <v>4.320532705448146</v>
       </c>
     </row>
     <row r="1808">
@@ -47450,7 +47450,7 @@
         <v>4.307185044668087</v>
       </c>
       <c r="H1808" t="n">
-        <v>4.342025204601791</v>
+        <v>4.342025204601793</v>
       </c>
     </row>
     <row r="1809">
@@ -47476,7 +47476,7 @@
         <v>4.317668080921759</v>
       </c>
       <c r="H1809" t="n">
-        <v>4.352665586966846</v>
+        <v>4.352665586966848</v>
       </c>
     </row>
     <row r="1810">
@@ -47502,7 +47502,7 @@
         <v>4.359774801914846</v>
       </c>
       <c r="H1810" t="n">
-        <v>4.396663741571127</v>
+        <v>4.396663741571129</v>
       </c>
     </row>
     <row r="1811">
@@ -47528,7 +47528,7 @@
         <v>4.375524660683229</v>
       </c>
       <c r="H1811" t="n">
-        <v>4.413763218978637</v>
+        <v>4.413763218978639</v>
       </c>
     </row>
     <row r="1812">
@@ -47554,7 +47554,7 @@
         <v>4.354776787967199</v>
       </c>
       <c r="H1812" t="n">
-        <v>4.392227061757884</v>
+        <v>4.392227061757886</v>
       </c>
     </row>
     <row r="1813">
@@ -47580,7 +47580,7 @@
         <v>4.381540759525391</v>
       </c>
       <c r="H1813" t="n">
-        <v>4.421548930487448</v>
+        <v>4.42154893048745</v>
       </c>
     </row>
     <row r="1814">
@@ -47606,7 +47606,7 @@
         <v>4.383129963829867</v>
       </c>
       <c r="H1814" t="n">
-        <v>4.423065246342463</v>
+        <v>4.423065246342465</v>
       </c>
     </row>
     <row r="1815">
@@ -47632,7 +47632,7 @@
         <v>4.388931276551237</v>
       </c>
       <c r="H1815" t="n">
-        <v>4.430051249714774</v>
+        <v>4.430051249714776</v>
       </c>
     </row>
     <row r="1816">
@@ -47658,7 +47658,7 @@
         <v>4.373405541088401</v>
       </c>
       <c r="H1816" t="n">
-        <v>4.41396795749988</v>
+        <v>4.413967957499882</v>
       </c>
     </row>
     <row r="1817">
@@ -47684,7 +47684,7 @@
         <v>4.393726553705108</v>
       </c>
       <c r="H1817" t="n">
-        <v>4.433700928841041</v>
+        <v>4.433700928841042</v>
       </c>
     </row>
     <row r="1818">
@@ -47710,7 +47710,7 @@
         <v>4.406233461569541</v>
       </c>
       <c r="H1818" t="n">
-        <v>4.446906528423668</v>
+        <v>4.44690652842367</v>
       </c>
     </row>
     <row r="1819">
@@ -47736,7 +47736,7 @@
         <v>4.378119484418455</v>
       </c>
       <c r="H1819" t="n">
-        <v>4.417791160493376</v>
+        <v>4.417791160493378</v>
       </c>
     </row>
     <row r="1820">
@@ -47762,7 +47762,7 @@
         <v>4.373147650784357</v>
       </c>
       <c r="H1820" t="n">
-        <v>4.41173306073185</v>
+        <v>4.411733060731851</v>
       </c>
     </row>
     <row r="1821">
@@ -47788,7 +47788,7 @@
         <v>4.380974952790542</v>
       </c>
       <c r="H1821" t="n">
-        <v>4.419314309422495</v>
+        <v>4.419314309422496</v>
       </c>
     </row>
     <row r="1822">
@@ -47814,7 +47814,7 @@
         <v>4.389459496430871</v>
       </c>
       <c r="H1822" t="n">
-        <v>4.427604967367037</v>
+        <v>4.427604967367039</v>
       </c>
     </row>
     <row r="1823">
@@ -47840,7 +47840,7 @@
         <v>4.37601599253553</v>
       </c>
       <c r="H1823" t="n">
-        <v>4.412944745634576</v>
+        <v>4.412944745634578</v>
       </c>
     </row>
     <row r="1824">
@@ -47866,7 +47866,7 @@
         <v>4.374940606209508</v>
       </c>
       <c r="H1824" t="n">
-        <v>4.410175227997609</v>
+        <v>4.410175227997611</v>
       </c>
     </row>
     <row r="1825">
@@ -47892,7 +47892,7 @@
         <v>4.383011912602987</v>
       </c>
       <c r="H1825" t="n">
-        <v>4.416287052463572</v>
+        <v>4.416287052463574</v>
       </c>
     </row>
     <row r="1826">
@@ -47918,7 +47918,7 @@
         <v>4.395519093736076</v>
       </c>
       <c r="H1826" t="n">
-        <v>4.428988465343476</v>
+        <v>4.428988465343478</v>
       </c>
     </row>
     <row r="1827">
@@ -47944,7 +47944,7 @@
         <v>4.40625106790713</v>
       </c>
       <c r="H1827" t="n">
-        <v>4.439748702866275</v>
+        <v>4.439748702866277</v>
       </c>
     </row>
     <row r="1828">
@@ -47970,7 +47970,7 @@
         <v>4.411319720533949</v>
       </c>
       <c r="H1828" t="n">
-        <v>4.445640278176427</v>
+        <v>4.445640278176429</v>
       </c>
     </row>
     <row r="1829">
@@ -47996,7 +47996,7 @@
         <v>4.416924600330325</v>
       </c>
       <c r="H1829" t="n">
-        <v>4.451060091291164</v>
+        <v>4.451060091291166</v>
       </c>
     </row>
     <row r="1830">
@@ -48022,7 +48022,7 @@
         <v>4.408497988547918</v>
       </c>
       <c r="H1830" t="n">
-        <v>4.441695541585381</v>
+        <v>4.441695541585383</v>
       </c>
     </row>
     <row r="1831">
@@ -48048,7 +48048,7 @@
         <v>4.409834210918142</v>
       </c>
       <c r="H1831" t="n">
-        <v>4.445307129057422</v>
+        <v>4.445307129057424</v>
       </c>
     </row>
     <row r="1832">
@@ -48074,7 +48074,7 @@
         <v>4.391664633321599</v>
       </c>
       <c r="H1832" t="n">
-        <v>4.427130771351473</v>
+        <v>4.427130771351475</v>
       </c>
     </row>
     <row r="1833">
@@ -48100,7 +48100,7 @@
         <v>4.38815269492885</v>
       </c>
       <c r="H1833" t="n">
-        <v>4.424526919062554</v>
+        <v>4.424526919062556</v>
       </c>
     </row>
     <row r="1834">
@@ -48126,7 +48126,7 @@
         <v>4.402066043680439</v>
       </c>
       <c r="H1834" t="n">
-        <v>4.439752823078281</v>
+        <v>4.439752823078282</v>
       </c>
     </row>
     <row r="1835">
@@ -48152,7 +48152,7 @@
         <v>4.392305852691392</v>
       </c>
       <c r="H1835" t="n">
-        <v>4.428909760086437</v>
+        <v>4.428909760086439</v>
       </c>
     </row>
     <row r="1836">
@@ -48178,7 +48178,7 @@
         <v>4.461867241074943</v>
       </c>
       <c r="H1836" t="n">
-        <v>4.498129010388196</v>
+        <v>4.498129010388197</v>
       </c>
     </row>
     <row r="1837">
@@ -48204,7 +48204,7 @@
         <v>4.464947446744465</v>
       </c>
       <c r="H1837" t="n">
-        <v>4.501774916454625</v>
+        <v>4.501774916454627</v>
       </c>
     </row>
     <row r="1838">
@@ -48230,7 +48230,7 @@
         <v>4.480408092106939</v>
       </c>
       <c r="H1838" t="n">
-        <v>4.51661739694913</v>
+        <v>4.516617396949131</v>
       </c>
     </row>
     <row r="1839">
@@ -48256,7 +48256,7 @@
         <v>4.49016510290593</v>
       </c>
       <c r="H1839" t="n">
-        <v>4.527414848445857</v>
+        <v>4.527414848445859</v>
       </c>
     </row>
     <row r="1840">
@@ -48282,7 +48282,7 @@
         <v>4.508224955938887</v>
       </c>
       <c r="H1840" t="n">
-        <v>4.5461413408879</v>
+        <v>4.546141340887901</v>
       </c>
     </row>
     <row r="1841">
@@ -48308,7 +48308,7 @@
         <v>4.53553524760823</v>
       </c>
       <c r="H1841" t="n">
-        <v>4.573469534119484</v>
+        <v>4.573469534119486</v>
       </c>
     </row>
     <row r="1842">
@@ -48334,7 +48334,7 @@
         <v>4.601417240304127</v>
       </c>
       <c r="H1842" t="n">
-        <v>4.635736893358693</v>
+        <v>4.635736893358695</v>
       </c>
     </row>
     <row r="1843">
@@ -48360,7 +48360,7 @@
         <v>4.597150925471943</v>
       </c>
       <c r="H1843" t="n">
-        <v>4.632847898750457</v>
+        <v>4.632847898750459</v>
       </c>
     </row>
     <row r="1844">
@@ -48386,7 +48386,7 @@
         <v>4.60079170081098</v>
       </c>
       <c r="H1844" t="n">
-        <v>4.635840757875225</v>
+        <v>4.635840757875227</v>
       </c>
     </row>
     <row r="1845">
@@ -48412,7 +48412,7 @@
         <v>4.58182947813213</v>
       </c>
       <c r="H1845" t="n">
-        <v>4.616744286357005</v>
+        <v>4.616744286357007</v>
       </c>
     </row>
     <row r="1846">
@@ -48438,7 +48438,7 @@
         <v>4.560152027612423</v>
       </c>
       <c r="H1846" t="n">
-        <v>4.595496957096285</v>
+        <v>4.595496957096286</v>
       </c>
     </row>
     <row r="1847">
@@ -48464,7 +48464,7 @@
         <v>4.578994633961251</v>
       </c>
       <c r="H1847" t="n">
-        <v>4.613360158639337</v>
+        <v>4.613360158639339</v>
       </c>
     </row>
     <row r="1848">
@@ -48490,7 +48490,7 @@
         <v>4.717843157518615</v>
       </c>
       <c r="H1848" t="n">
-        <v>4.75061223203567</v>
+        <v>4.750612232035672</v>
       </c>
     </row>
     <row r="1849">
@@ -48516,7 +48516,7 @@
         <v>4.72939814224161</v>
       </c>
       <c r="H1849" t="n">
-        <v>4.76225156390919</v>
+        <v>4.762251563909192</v>
       </c>
     </row>
     <row r="1850">
@@ -48542,7 +48542,7 @@
         <v>4.731138637829968</v>
       </c>
       <c r="H1850" t="n">
-        <v>4.763075438794914</v>
+        <v>4.763075438794916</v>
       </c>
     </row>
     <row r="1851">
@@ -48568,7 +48568,7 @@
         <v>4.726267130704385</v>
       </c>
       <c r="H1851" t="n">
-        <v>4.758054469040522</v>
+        <v>4.758054469040523</v>
       </c>
     </row>
     <row r="1852">
@@ -48594,7 +48594,7 @@
         <v>4.695328177691437</v>
       </c>
       <c r="H1852" t="n">
-        <v>4.727765572388262</v>
+        <v>4.727765572388264</v>
       </c>
     </row>
     <row r="1853">
@@ -48620,7 +48620,7 @@
         <v>4.766496214821863</v>
       </c>
       <c r="H1853" t="n">
-        <v>4.79967525330966</v>
+        <v>4.799675253309662</v>
       </c>
     </row>
     <row r="1854">
@@ -48646,7 +48646,7 @@
         <v>4.745464279779531</v>
       </c>
       <c r="H1854" t="n">
-        <v>4.777978679356233</v>
+        <v>4.777978679356234</v>
       </c>
     </row>
     <row r="1855">
@@ -48672,7 +48672,7 @@
         <v>4.749863586351658</v>
       </c>
       <c r="H1855" t="n">
-        <v>4.784661255933226</v>
+        <v>4.784661255933227</v>
       </c>
     </row>
     <row r="1856">
@@ -48698,7 +48698,7 @@
         <v>4.735075463249443</v>
       </c>
       <c r="H1856" t="n">
-        <v>4.768399508231026</v>
+        <v>4.768399508231028</v>
       </c>
     </row>
     <row r="1857">
@@ -48724,7 +48724,7 @@
         <v>4.757256316012661</v>
       </c>
       <c r="H1857" t="n">
-        <v>4.790279797770702</v>
+        <v>4.790279797770704</v>
       </c>
     </row>
     <row r="1858">
@@ -48750,7 +48750,7 @@
         <v>4.716204228875381</v>
       </c>
       <c r="H1858" t="n">
-        <v>4.749417385742077</v>
+        <v>4.749417385742079</v>
       </c>
     </row>
     <row r="1859">
@@ -48776,7 +48776,7 @@
         <v>4.714862162973803</v>
       </c>
       <c r="H1859" t="n">
-        <v>4.746806176929486</v>
+        <v>4.746806176929487</v>
       </c>
     </row>
     <row r="1860">
@@ -48802,7 +48802,7 @@
         <v>4.736483456502151</v>
       </c>
       <c r="H1860" t="n">
-        <v>4.771083163057924</v>
+        <v>4.771083163057925</v>
       </c>
     </row>
     <row r="1861">
@@ -48828,7 +48828,7 @@
         <v>4.732230814986101</v>
       </c>
       <c r="H1861" t="n">
-        <v>4.766916791011067</v>
+        <v>4.766916791011068</v>
       </c>
     </row>
     <row r="1862">
@@ -48854,7 +48854,7 @@
         <v>4.74909216185914</v>
       </c>
       <c r="H1862" t="n">
-        <v>4.783366605273378</v>
+        <v>4.78336660527338</v>
       </c>
     </row>
     <row r="1863">
@@ -48880,7 +48880,7 @@
         <v>4.735785663248535</v>
       </c>
       <c r="H1863" t="n">
-        <v>4.767905649070877</v>
+        <v>4.767905649070879</v>
       </c>
     </row>
     <row r="1864">
@@ -48906,7 +48906,7 @@
         <v>4.708809840198299</v>
       </c>
       <c r="H1864" t="n">
-        <v>4.740774781489628</v>
+        <v>4.740774781489629</v>
       </c>
     </row>
     <row r="1865">
@@ -48932,7 +48932,7 @@
         <v>4.698036350270575</v>
       </c>
       <c r="H1865" t="n">
-        <v>4.730335840629568</v>
+        <v>4.73033584062957</v>
       </c>
     </row>
     <row r="1866">
@@ -48958,7 +48958,7 @@
         <v>4.721599131447088</v>
       </c>
       <c r="H1866" t="n">
-        <v>4.754417884959811</v>
+        <v>4.754417884959813</v>
       </c>
     </row>
     <row r="1867">
@@ -48984,7 +48984,7 @@
         <v>4.687423372209106</v>
       </c>
       <c r="H1867" t="n">
-        <v>4.721963835952097</v>
+        <v>4.721963835952099</v>
       </c>
     </row>
     <row r="1868">
@@ -49010,7 +49010,7 @@
         <v>4.641847560446966</v>
       </c>
       <c r="H1868" t="n">
-        <v>4.678183405517408</v>
+        <v>4.67818340551741</v>
       </c>
     </row>
     <row r="1869">
@@ -49036,7 +49036,7 @@
         <v>4.633895671992629</v>
       </c>
       <c r="H1869" t="n">
-        <v>4.670633684668496</v>
+        <v>4.670633684668497</v>
       </c>
     </row>
     <row r="1870">
@@ -49062,7 +49062,7 @@
         <v>4.652936063465128</v>
       </c>
       <c r="H1870" t="n">
-        <v>4.689394808979528</v>
+        <v>4.68939480897953</v>
       </c>
     </row>
     <row r="1871">
@@ -49088,7 +49088,7 @@
         <v>4.64408220392683</v>
       </c>
       <c r="H1871" t="n">
-        <v>4.680505516767843</v>
+        <v>4.680505516767845</v>
       </c>
     </row>
     <row r="1872">
@@ -49114,7 +49114,7 @@
         <v>4.639085659744943</v>
       </c>
       <c r="H1872" t="n">
-        <v>4.677018675120927</v>
+        <v>4.677018675120928</v>
       </c>
     </row>
     <row r="1873">
@@ -49140,7 +49140,7 @@
         <v>4.652532112212449</v>
       </c>
       <c r="H1873" t="n">
-        <v>4.68958171731104</v>
+        <v>4.689581717311042</v>
       </c>
     </row>
     <row r="1874">
@@ -49166,7 +49166,7 @@
         <v>4.692929154232257</v>
       </c>
       <c r="H1874" t="n">
-        <v>4.729906998961635</v>
+        <v>4.729906998961637</v>
       </c>
     </row>
     <row r="1875">
@@ -49192,7 +49192,7 @@
         <v>4.673074160384008</v>
       </c>
       <c r="H1875" t="n">
-        <v>4.708570757237445</v>
+        <v>4.708570757237447</v>
       </c>
     </row>
     <row r="1876">
@@ -49218,7 +49218,7 @@
         <v>4.722760239452658</v>
       </c>
       <c r="H1876" t="n">
-        <v>4.755721274520773</v>
+        <v>4.755721274520774</v>
       </c>
     </row>
     <row r="1877">
@@ -49244,7 +49244,7 @@
         <v>4.716776141387707</v>
       </c>
       <c r="H1877" t="n">
-        <v>4.751333645626155</v>
+        <v>4.751333645626157</v>
       </c>
     </row>
     <row r="1878">
@@ -49270,7 +49270,7 @@
         <v>4.715573702008927</v>
       </c>
       <c r="H1878" t="n">
-        <v>4.749902653083783</v>
+        <v>4.749902653083785</v>
       </c>
     </row>
     <row r="1879">
@@ -49296,7 +49296,7 @@
         <v>4.735771402794715</v>
       </c>
       <c r="H1879" t="n">
-        <v>4.769688940430059</v>
+        <v>4.76968894043006</v>
       </c>
     </row>
     <row r="1880">
@@ -49322,7 +49322,7 @@
         <v>4.708903128657059</v>
       </c>
       <c r="H1880" t="n">
-        <v>4.743354183720374</v>
+        <v>4.743354183720376</v>
       </c>
     </row>
     <row r="1881">
@@ -49348,7 +49348,7 @@
         <v>4.693738421568314</v>
       </c>
       <c r="H1881" t="n">
-        <v>4.728066699098823</v>
+        <v>4.728066699098825</v>
       </c>
     </row>
     <row r="1882">
@@ -49374,7 +49374,7 @@
         <v>4.688792632763806</v>
       </c>
       <c r="H1882" t="n">
-        <v>4.724332163685922</v>
+        <v>4.724332163685924</v>
       </c>
     </row>
     <row r="1883">
@@ -49400,7 +49400,7 @@
         <v>4.65057989541485</v>
       </c>
       <c r="H1883" t="n">
-        <v>4.685673426866046</v>
+        <v>4.685673426866048</v>
       </c>
     </row>
     <row r="1884">
@@ -49426,7 +49426,7 @@
         <v>4.641485944811228</v>
       </c>
       <c r="H1884" t="n">
-        <v>4.675937317573034</v>
+        <v>4.675937317573036</v>
       </c>
     </row>
     <row r="1885">
@@ -49452,7 +49452,7 @@
         <v>4.660188164515705</v>
       </c>
       <c r="H1885" t="n">
-        <v>4.695571374386818</v>
+        <v>4.695571374386819</v>
       </c>
     </row>
     <row r="1886">
@@ -49478,7 +49478,7 @@
         <v>4.668606734722598</v>
       </c>
       <c r="H1886" t="n">
-        <v>4.703703224280363</v>
+        <v>4.703703224280365</v>
       </c>
     </row>
     <row r="1887">
@@ -49504,7 +49504,7 @@
         <v>4.644377735203593</v>
       </c>
       <c r="H1887" t="n">
-        <v>4.679591049657621</v>
+        <v>4.679591049657622</v>
       </c>
     </row>
     <row r="1888">
@@ -49530,7 +49530,7 @@
         <v>4.654486669574633</v>
       </c>
       <c r="H1888" t="n">
-        <v>4.690149448162774</v>
+        <v>4.690149448162776</v>
       </c>
     </row>
     <row r="1889">
@@ -49556,7 +49556,7 @@
         <v>4.651882446464077</v>
       </c>
       <c r="H1889" t="n">
-        <v>4.687244887357238</v>
+        <v>4.68724488735724</v>
       </c>
     </row>
     <row r="1890">
@@ -49582,7 +49582,7 @@
         <v>4.62084946440907</v>
       </c>
       <c r="H1890" t="n">
-        <v>4.655146149984546</v>
+        <v>4.655146149984548</v>
       </c>
     </row>
     <row r="1891">
@@ -49608,7 +49608,7 @@
         <v>4.606960653963472</v>
       </c>
       <c r="H1891" t="n">
-        <v>4.640933037481784</v>
+        <v>4.640933037481786</v>
       </c>
     </row>
     <row r="1892">
@@ -49634,7 +49634,7 @@
         <v>4.608671538394951</v>
       </c>
       <c r="H1892" t="n">
-        <v>4.644039548007076</v>
+        <v>4.644039548007078</v>
       </c>
     </row>
     <row r="1893">
@@ -49660,7 +49660,7 @@
         <v>4.607567387587554</v>
       </c>
       <c r="H1893" t="n">
-        <v>4.643279721959162</v>
+        <v>4.643279721959164</v>
       </c>
     </row>
     <row r="1894">
@@ -49686,7 +49686,7 @@
         <v>4.599366840989798</v>
       </c>
       <c r="H1894" t="n">
-        <v>4.634832229668066</v>
+        <v>4.634832229668068</v>
       </c>
     </row>
     <row r="1895">
@@ -49712,7 +49712,7 @@
         <v>4.601776049353912</v>
       </c>
       <c r="H1895" t="n">
-        <v>4.637684850550215</v>
+        <v>4.637684850550217</v>
       </c>
     </row>
     <row r="1896">
@@ -49738,7 +49738,7 @@
         <v>4.565447405016003</v>
       </c>
       <c r="H1896" t="n">
-        <v>4.599402096370006</v>
+        <v>4.599402096370008</v>
       </c>
     </row>
     <row r="1897">
@@ -49764,7 +49764,7 @@
         <v>4.545782905626002</v>
       </c>
       <c r="H1897" t="n">
-        <v>4.578271808718148</v>
+        <v>4.578271808718149</v>
       </c>
     </row>
     <row r="1898">
@@ -49790,7 +49790,7 @@
         <v>4.540123887578353</v>
       </c>
       <c r="H1898" t="n">
-        <v>4.571897231651205</v>
+        <v>4.571897231651207</v>
       </c>
     </row>
     <row r="1899">
@@ -49816,7 +49816,7 @@
         <v>4.54691994181721</v>
       </c>
       <c r="H1899" t="n">
-        <v>4.579464797428353</v>
+        <v>4.579464797428355</v>
       </c>
     </row>
     <row r="1900">
@@ -49842,7 +49842,7 @@
         <v>4.59012463170846</v>
       </c>
       <c r="H1900" t="n">
-        <v>4.621798166236132</v>
+        <v>4.621798166236133</v>
       </c>
     </row>
     <row r="1901">
@@ -49868,7 +49868,7 @@
         <v>4.596859685025397</v>
       </c>
       <c r="H1901" t="n">
-        <v>4.630162077800704</v>
+        <v>4.630162077800706</v>
       </c>
     </row>
     <row r="1902">
@@ -49894,7 +49894,7 @@
         <v>4.587186453909527</v>
       </c>
       <c r="H1902" t="n">
-        <v>4.620493613413638</v>
+        <v>4.62049361341364</v>
       </c>
     </row>
     <row r="1903">
@@ -49920,7 +49920,7 @@
         <v>4.610947045318051</v>
       </c>
       <c r="H1903" t="n">
-        <v>4.643041343744137</v>
+        <v>4.643041343744139</v>
       </c>
     </row>
     <row r="1904">
@@ -49946,7 +49946,7 @@
         <v>4.658065206515539</v>
       </c>
       <c r="H1904" t="n">
-        <v>4.690484393623199</v>
+        <v>4.690484393623201</v>
       </c>
     </row>
     <row r="1905">
@@ -49972,7 +49972,7 @@
         <v>4.646431920906068</v>
       </c>
       <c r="H1905" t="n">
-        <v>4.678666274537267</v>
+        <v>4.678666274537269</v>
       </c>
     </row>
     <row r="1906">
@@ -49998,7 +49998,7 @@
         <v>4.672851843091741</v>
       </c>
       <c r="H1906" t="n">
-        <v>4.704687558163997</v>
+        <v>4.704687558163998</v>
       </c>
     </row>
     <row r="1907">
@@ -50024,7 +50024,7 @@
         <v>4.668804225873188</v>
       </c>
       <c r="H1907" t="n">
-        <v>4.700436004910156</v>
+        <v>4.700436004910157</v>
       </c>
     </row>
     <row r="1908">
@@ -50050,7 +50050,7 @@
         <v>4.658530831075407</v>
       </c>
       <c r="H1908" t="n">
-        <v>4.686541881408424</v>
+        <v>4.686541881408425</v>
       </c>
     </row>
     <row r="1909">
@@ -50076,7 +50076,7 @@
         <v>4.615584023263761</v>
       </c>
       <c r="H1909" t="n">
-        <v>4.644556551558201</v>
+        <v>4.644556551558203</v>
       </c>
     </row>
     <row r="1910">
@@ -50102,7 +50102,7 @@
         <v>4.639593875024922</v>
       </c>
       <c r="H1910" t="n">
-        <v>4.667686619287073</v>
+        <v>4.667686619287075</v>
       </c>
     </row>
     <row r="1911">
@@ -50128,7 +50128,7 @@
         <v>4.619906772379233</v>
       </c>
       <c r="H1911" t="n">
-        <v>4.649288033056548</v>
+        <v>4.64928803305655</v>
       </c>
     </row>
     <row r="1912">
@@ -50154,7 +50154,7 @@
         <v>4.633422761049601</v>
       </c>
       <c r="H1912" t="n">
-        <v>4.662857133687846</v>
+        <v>4.662857133687848</v>
       </c>
     </row>
     <row r="1913">
@@ -50180,7 +50180,7 @@
         <v>4.641021364850717</v>
       </c>
       <c r="H1913" t="n">
-        <v>4.670096337367389</v>
+        <v>4.670096337367391</v>
       </c>
     </row>
     <row r="1914">
@@ -50206,7 +50206,7 @@
         <v>4.63892480332807</v>
       </c>
       <c r="H1914" t="n">
-        <v>4.668290647941284</v>
+        <v>4.668290647941285</v>
       </c>
     </row>
     <row r="1915">
@@ -50232,7 +50232,7 @@
         <v>4.657305492678628</v>
       </c>
       <c r="H1915" t="n">
-        <v>4.68546513527903</v>
+        <v>4.685465135279031</v>
       </c>
     </row>
     <row r="1916">
@@ -50258,7 +50258,7 @@
         <v>4.68665843491077</v>
       </c>
       <c r="H1916" t="n">
-        <v>4.714614214467119</v>
+        <v>4.714614214467121</v>
       </c>
     </row>
     <row r="1917">
@@ -50284,7 +50284,7 @@
         <v>4.691628302477348</v>
       </c>
       <c r="H1917" t="n">
-        <v>4.719599873323894</v>
+        <v>4.719599873323896</v>
       </c>
     </row>
     <row r="1918">
@@ -50310,7 +50310,7 @@
         <v>4.715758421159182</v>
       </c>
       <c r="H1918" t="n">
-        <v>4.74361012133298</v>
+        <v>4.743610121332982</v>
       </c>
     </row>
     <row r="1919">
@@ -50336,7 +50336,7 @@
         <v>4.692434014095372</v>
       </c>
       <c r="H1919" t="n">
-        <v>4.721252124130733</v>
+        <v>4.721252124130735</v>
       </c>
     </row>
     <row r="1920">
@@ -50362,7 +50362,7 @@
         <v>4.689856209530431</v>
       </c>
       <c r="H1920" t="n">
-        <v>4.717758894783026</v>
+        <v>4.717758894783028</v>
       </c>
     </row>
     <row r="1921">
@@ -50388,7 +50388,7 @@
         <v>4.665045028556302</v>
       </c>
       <c r="H1921" t="n">
-        <v>4.691784448932493</v>
+        <v>4.691784448932495</v>
       </c>
     </row>
     <row r="1922">
@@ -50414,7 +50414,7 @@
         <v>4.658204680611495</v>
       </c>
       <c r="H1922" t="n">
-        <v>4.684505968727968</v>
+        <v>4.68450596872797</v>
       </c>
     </row>
     <row r="1923">
@@ -50440,7 +50440,7 @@
         <v>4.654897186289745</v>
       </c>
       <c r="H1923" t="n">
-        <v>4.68110727331084</v>
+        <v>4.681107273310841</v>
       </c>
     </row>
     <row r="1924">
@@ -50466,7 +50466,7 @@
         <v>4.639185884276947</v>
       </c>
       <c r="H1924" t="n">
-        <v>4.666395983726861</v>
+        <v>4.666395983726863</v>
       </c>
     </row>
     <row r="1925">
@@ -50492,7 +50492,7 @@
         <v>4.64041192927153</v>
       </c>
       <c r="H1925" t="n">
-        <v>4.668220523930932</v>
+        <v>4.668220523930934</v>
       </c>
     </row>
     <row r="1926">
@@ -50518,7 +50518,7 @@
         <v>4.633700930049829</v>
       </c>
       <c r="H1926" t="n">
-        <v>4.66139637165661</v>
+        <v>4.661396371656612</v>
       </c>
     </row>
     <row r="1927">
@@ -50544,7 +50544,7 @@
         <v>4.642855152841918</v>
       </c>
       <c r="H1927" t="n">
-        <v>4.67032492848905</v>
+        <v>4.670324928489052</v>
       </c>
     </row>
     <row r="1928">
@@ -50570,7 +50570,7 @@
         <v>4.664590688634217</v>
       </c>
       <c r="H1928" t="n">
-        <v>4.69212527049791</v>
+        <v>4.692125270497912</v>
       </c>
     </row>
     <row r="1929">
@@ -50596,7 +50596,7 @@
         <v>4.669503746717664</v>
       </c>
       <c r="H1929" t="n">
-        <v>4.696267555718727</v>
+        <v>4.696267555718729</v>
       </c>
     </row>
     <row r="1930">
@@ -50622,7 +50622,7 @@
         <v>4.665153724532002</v>
       </c>
       <c r="H1930" t="n">
-        <v>4.691935029358085</v>
+        <v>4.691935029358087</v>
       </c>
     </row>
     <row r="1931">
@@ -50648,7 +50648,7 @@
         <v>4.668364797594479</v>
       </c>
       <c r="H1931" t="n">
-        <v>4.693861524564593</v>
+        <v>4.693861524564594</v>
       </c>
     </row>
     <row r="1932">
@@ -50674,7 +50674,7 @@
         <v>4.676107638576394</v>
       </c>
       <c r="H1932" t="n">
-        <v>4.701577432558706</v>
+        <v>4.701577432558707</v>
       </c>
     </row>
     <row r="1933">
@@ -50700,7 +50700,7 @@
         <v>4.675944321949097</v>
       </c>
       <c r="H1933" t="n">
-        <v>4.701075174313761</v>
+        <v>4.701075174313763</v>
       </c>
     </row>
     <row r="1934">
@@ -50726,7 +50726,7 @@
         <v>4.680018792740334</v>
       </c>
       <c r="H1934" t="n">
-        <v>4.704526461702859</v>
+        <v>4.70452646170286</v>
       </c>
     </row>
     <row r="1935">
@@ -50752,7 +50752,7 @@
         <v>4.660929277188344</v>
       </c>
       <c r="H1935" t="n">
-        <v>4.686555033305315</v>
+        <v>4.686555033305317</v>
       </c>
     </row>
     <row r="1936">
@@ -50778,7 +50778,7 @@
         <v>4.699183538192226</v>
       </c>
       <c r="H1936" t="n">
-        <v>4.725732484800549</v>
+        <v>4.725732484800551</v>
       </c>
     </row>
     <row r="1937">
@@ -50804,7 +50804,7 @@
         <v>4.626553181211167</v>
       </c>
       <c r="H1937" t="n">
-        <v>4.65448217039201</v>
+        <v>4.654482170392011</v>
       </c>
     </row>
     <row r="1938">
@@ -50830,7 +50830,7 @@
         <v>4.596393601037327</v>
       </c>
       <c r="H1938" t="n">
-        <v>4.625631904728026</v>
+        <v>4.625631904728028</v>
       </c>
     </row>
     <row r="1939">
@@ -50856,7 +50856,7 @@
         <v>4.560372250254806</v>
       </c>
       <c r="H1939" t="n">
-        <v>4.58876524063843</v>
+        <v>4.588765240638431</v>
       </c>
     </row>
     <row r="1940">
@@ -50882,7 +50882,7 @@
         <v>4.569052182366809</v>
       </c>
       <c r="H1940" t="n">
-        <v>4.596117773628854</v>
+        <v>4.596117773628856</v>
       </c>
     </row>
     <row r="1941">
@@ -50908,7 +50908,7 @@
         <v>4.560471342393376</v>
       </c>
       <c r="H1941" t="n">
-        <v>4.58716176060214</v>
+        <v>4.587161760602141</v>
       </c>
     </row>
     <row r="1942">
@@ -50934,7 +50934,7 @@
         <v>4.554861161088983</v>
       </c>
       <c r="H1942" t="n">
-        <v>4.582627940508091</v>
+        <v>4.582627940508093</v>
       </c>
     </row>
     <row r="1943">
@@ -50960,7 +50960,7 @@
         <v>4.570574843953479</v>
       </c>
       <c r="H1943" t="n">
-        <v>4.598677965659949</v>
+        <v>4.598677965659951</v>
       </c>
     </row>
     <row r="1944">
@@ -50986,7 +50986,7 @@
         <v>4.569706293240746</v>
       </c>
       <c r="H1944" t="n">
-        <v>4.597911230622127</v>
+        <v>4.597911230622128</v>
       </c>
     </row>
     <row r="1945">
@@ -51012,7 +51012,7 @@
         <v>4.594909823751991</v>
       </c>
       <c r="H1945" t="n">
-        <v>4.623439403192316</v>
+        <v>4.623439403192318</v>
       </c>
     </row>
     <row r="1946">
@@ -51038,7 +51038,7 @@
         <v>4.601146872812323</v>
       </c>
       <c r="H1946" t="n">
-        <v>4.629067420175527</v>
+        <v>4.629067420175529</v>
       </c>
     </row>
     <row r="1947">
@@ -51064,7 +51064,7 @@
         <v>4.60455461974126</v>
       </c>
       <c r="H1947" t="n">
-        <v>4.633560241172544</v>
+        <v>4.633560241172546</v>
       </c>
     </row>
     <row r="1948">
@@ -51090,7 +51090,7 @@
         <v>4.602882194357579</v>
       </c>
       <c r="H1948" t="n">
-        <v>4.631120820086119</v>
+        <v>4.631120820086121</v>
       </c>
     </row>
     <row r="1949">
@@ -51116,7 +51116,7 @@
         <v>4.556212055065675</v>
       </c>
       <c r="H1949" t="n">
-        <v>4.584554859853224</v>
+        <v>4.584554859853226</v>
       </c>
     </row>
     <row r="1950">
@@ -51142,7 +51142,7 @@
         <v>4.556140383185803</v>
       </c>
       <c r="H1950" t="n">
-        <v>4.583603871049961</v>
+        <v>4.583603871049963</v>
       </c>
     </row>
     <row r="1951">
@@ -51168,7 +51168,7 @@
         <v>4.564037367841594</v>
       </c>
       <c r="H1951" t="n">
-        <v>4.59138536530686</v>
+        <v>4.591385365306862</v>
       </c>
     </row>
     <row r="1952">
@@ -51194,7 +51194,7 @@
         <v>4.564009293844171</v>
       </c>
       <c r="H1952" t="n">
-        <v>4.590845261145399</v>
+        <v>4.590845261145401</v>
       </c>
     </row>
     <row r="1953">
@@ -51220,7 +51220,7 @@
         <v>4.573982078002266</v>
       </c>
       <c r="H1953" t="n">
-        <v>4.600455088983021</v>
+        <v>4.600455088983023</v>
       </c>
     </row>
     <row r="1954">
@@ -51246,7 +51246,7 @@
         <v>4.55767227781192</v>
       </c>
       <c r="H1954" t="n">
-        <v>4.584151956134161</v>
+        <v>4.584151956134163</v>
       </c>
     </row>
     <row r="1955">
@@ -51272,7 +51272,7 @@
         <v>4.54960536319993</v>
       </c>
       <c r="H1955" t="n">
-        <v>4.576103501976857</v>
+        <v>4.576103501976859</v>
       </c>
     </row>
     <row r="1956">
@@ -51298,7 +51298,7 @@
         <v>4.546436428482233</v>
       </c>
       <c r="H1956" t="n">
-        <v>4.573012010896708</v>
+        <v>4.57301201089671</v>
       </c>
     </row>
     <row r="1957">
@@ -51324,7 +51324,7 @@
         <v>4.549868817267415</v>
       </c>
       <c r="H1957" t="n">
-        <v>4.576996549559655</v>
+        <v>4.576996549559657</v>
       </c>
     </row>
     <row r="1958">
@@ -51350,7 +51350,7 @@
         <v>4.532492643865637</v>
       </c>
       <c r="H1958" t="n">
-        <v>4.55995818028379</v>
+        <v>4.559958180283791</v>
       </c>
     </row>
     <row r="1959">
@@ -51376,7 +51376,7 @@
         <v>4.522329520991194</v>
       </c>
       <c r="H1959" t="n">
-        <v>4.550359402190523</v>
+        <v>4.550359402190525</v>
       </c>
     </row>
     <row r="1960">
@@ -51402,7 +51402,7 @@
         <v>4.518644460962261</v>
       </c>
       <c r="H1960" t="n">
-        <v>4.546642626896404</v>
+        <v>4.546642626896406</v>
       </c>
     </row>
     <row r="1961">
@@ -51428,7 +51428,7 @@
         <v>4.52264775886145</v>
       </c>
       <c r="H1961" t="n">
-        <v>4.55309206528386</v>
+        <v>4.553092065283862</v>
       </c>
     </row>
     <row r="1962">
@@ -51454,7 +51454,7 @@
         <v>4.523322030731044</v>
       </c>
       <c r="H1962" t="n">
-        <v>4.553404267012047</v>
+        <v>4.553404267012048</v>
       </c>
     </row>
     <row r="1963">
@@ -51480,7 +51480,7 @@
         <v>4.525362655980738</v>
       </c>
       <c r="H1963" t="n">
-        <v>4.555786296237514</v>
+        <v>4.555786296237516</v>
       </c>
     </row>
     <row r="1964">
@@ -51506,7 +51506,7 @@
         <v>4.52801262378909</v>
       </c>
       <c r="H1964" t="n">
-        <v>4.558424372649169</v>
+        <v>4.558424372649171</v>
       </c>
     </row>
     <row r="1965">
@@ -51532,7 +51532,7 @@
         <v>4.534102622210985</v>
       </c>
       <c r="H1965" t="n">
-        <v>4.562601219051742</v>
+        <v>4.562601219051744</v>
       </c>
     </row>
     <row r="1966">
@@ -51558,7 +51558,7 @@
         <v>4.518661550983175</v>
       </c>
       <c r="H1966" t="n">
-        <v>4.547497788748282</v>
+        <v>4.547497788748283</v>
       </c>
     </row>
     <row r="1967">
@@ -51584,7 +51584,7 @@
         <v>4.522767710677211</v>
       </c>
       <c r="H1967" t="n">
-        <v>4.552151377124249</v>
+        <v>4.55215137712425</v>
       </c>
     </row>
     <row r="1968">
@@ -51610,7 +51610,7 @@
         <v>4.530731671367869</v>
       </c>
       <c r="H1968" t="n">
-        <v>4.559490931210341</v>
+        <v>4.559490931210343</v>
       </c>
     </row>
     <row r="1969">
@@ -51636,7 +51636,7 @@
         <v>4.539468231164546</v>
       </c>
       <c r="H1969" t="n">
-        <v>4.566666013296441</v>
+        <v>4.566666013296443</v>
       </c>
     </row>
     <row r="1970">
@@ -51662,7 +51662,7 @@
         <v>4.545053941694123</v>
       </c>
       <c r="H1970" t="n">
-        <v>4.570702395053095</v>
+        <v>4.570702395053097</v>
       </c>
     </row>
     <row r="1971">
@@ -51688,7 +51688,7 @@
         <v>4.552194089479513</v>
       </c>
       <c r="H1971" t="n">
-        <v>4.577254438265198</v>
+        <v>4.5772544382652</v>
       </c>
     </row>
     <row r="1972">
@@ -51714,7 +51714,7 @@
         <v>4.526113937994415</v>
       </c>
       <c r="H1972" t="n">
-        <v>4.551681337645609</v>
+        <v>4.55168133764561</v>
       </c>
     </row>
     <row r="1973">
@@ -51740,7 +51740,7 @@
         <v>4.531667027898074</v>
       </c>
       <c r="H1973" t="n">
-        <v>4.556327601647702</v>
+        <v>4.556327601647704</v>
       </c>
     </row>
     <row r="1974">
@@ -51766,7 +51766,7 @@
         <v>4.534378131779228</v>
       </c>
       <c r="H1974" t="n">
-        <v>4.558448306625688</v>
+        <v>4.55844830662569</v>
       </c>
     </row>
     <row r="1975">
@@ -51792,7 +51792,7 @@
         <v>4.536980184628913</v>
       </c>
       <c r="H1975" t="n">
-        <v>4.56061328349056</v>
+        <v>4.560613283490562</v>
       </c>
     </row>
     <row r="1976">
@@ -51818,7 +51818,7 @@
         <v>4.552977759762523</v>
       </c>
       <c r="H1976" t="n">
-        <v>4.577080266078997</v>
+        <v>4.577080266078998</v>
       </c>
     </row>
     <row r="1977">
@@ -51844,7 +51844,7 @@
         <v>4.547406331201516</v>
       </c>
       <c r="H1977" t="n">
-        <v>4.570947532285808</v>
+        <v>4.57094753228581</v>
       </c>
     </row>
     <row r="1978">
@@ -51870,7 +51870,7 @@
         <v>4.563271726721504</v>
       </c>
       <c r="H1978" t="n">
-        <v>4.585865370347298</v>
+        <v>4.5858653703473</v>
       </c>
     </row>
     <row r="1979">
@@ -51896,7 +51896,7 @@
         <v>4.552072548856589</v>
       </c>
       <c r="H1979" t="n">
-        <v>4.573661601845733</v>
+        <v>4.573661601845735</v>
       </c>
     </row>
     <row r="1980">
@@ -51922,7 +51922,7 @@
         <v>4.544969300934181</v>
       </c>
       <c r="H1980" t="n">
-        <v>4.566639382936468</v>
+        <v>4.56663938293647</v>
       </c>
     </row>
     <row r="1981">
@@ -51948,7 +51948,7 @@
         <v>4.573545852454198</v>
       </c>
       <c r="H1981" t="n">
-        <v>4.594309068057468</v>
+        <v>4.59430906805747</v>
       </c>
     </row>
     <row r="1982">
@@ -51974,7 +51974,7 @@
         <v>4.559685163283847</v>
       </c>
       <c r="H1982" t="n">
-        <v>4.57938914930951</v>
+        <v>4.579389149309512</v>
       </c>
     </row>
     <row r="1983">
@@ -52000,7 +52000,7 @@
         <v>4.560928178558033</v>
       </c>
       <c r="H1983" t="n">
-        <v>4.580204776437798</v>
+        <v>4.5802047764378</v>
       </c>
     </row>
     <row r="1984">
@@ -52026,7 +52026,7 @@
         <v>4.527302582292873</v>
       </c>
       <c r="H1984" t="n">
-        <v>4.548295458201535</v>
+        <v>4.548295458201537</v>
       </c>
     </row>
     <row r="1985">
@@ -52052,7 +52052,7 @@
         <v>4.549192276842525</v>
       </c>
       <c r="H1985" t="n">
-        <v>4.570849567955792</v>
+        <v>4.570849567955793</v>
       </c>
     </row>
     <row r="1986">
@@ -52078,7 +52078,7 @@
         <v>4.547780763206204</v>
       </c>
       <c r="H1986" t="n">
-        <v>4.570467969206341</v>
+        <v>4.570467969206343</v>
       </c>
     </row>
     <row r="1987">
@@ -52104,7 +52104,7 @@
         <v>4.548724581363529</v>
       </c>
       <c r="H1987" t="n">
-        <v>4.570902522647187</v>
+        <v>4.570902522647189</v>
       </c>
     </row>
     <row r="1988">
@@ -52130,7 +52130,7 @@
         <v>4.559804997612229</v>
       </c>
       <c r="H1988" t="n">
-        <v>4.584638585356906</v>
+        <v>4.584638585356908</v>
       </c>
     </row>
     <row r="1989">
@@ -52156,7 +52156,7 @@
         <v>4.559307057591142</v>
       </c>
       <c r="H1989" t="n">
-        <v>4.583802321296401</v>
+        <v>4.583802321296403</v>
       </c>
     </row>
     <row r="1990">
@@ -52182,7 +52182,7 @@
         <v>4.567355857660326</v>
       </c>
       <c r="H1990" t="n">
-        <v>4.590987648642601</v>
+        <v>4.590987648642603</v>
       </c>
     </row>
     <row r="1991">
@@ -52208,7 +52208,7 @@
         <v>4.568514349473253</v>
       </c>
       <c r="H1991" t="n">
-        <v>4.592845844254874</v>
+        <v>4.592845844254875</v>
       </c>
     </row>
     <row r="1992">
@@ -52234,7 +52234,7 @@
         <v>4.556354717923479</v>
       </c>
       <c r="H1992" t="n">
-        <v>4.580670359828837</v>
+        <v>4.580670359828839</v>
       </c>
     </row>
     <row r="1993">
@@ -52260,7 +52260,7 @@
         <v>4.528572026440194</v>
       </c>
       <c r="H1993" t="n">
-        <v>4.5543618116114</v>
+        <v>4.554361811611401</v>
       </c>
     </row>
     <row r="1994">
@@ -52286,7 +52286,7 @@
         <v>4.538942898048217</v>
       </c>
       <c r="H1994" t="n">
-        <v>4.566428019537804</v>
+        <v>4.566428019537806</v>
       </c>
     </row>
     <row r="1995">
@@ -52312,7 +52312,7 @@
         <v>4.549253702333744</v>
       </c>
       <c r="H1995" t="n">
-        <v>4.577136092774267</v>
+        <v>4.577136092774269</v>
       </c>
     </row>
     <row r="1996">
@@ -52338,7 +52338,7 @@
         <v>4.542912986752136</v>
       </c>
       <c r="H1996" t="n">
-        <v>4.570546354875901</v>
+        <v>4.570546354875903</v>
       </c>
     </row>
     <row r="1997">
@@ -52364,7 +52364,7 @@
         <v>4.545452934462922</v>
       </c>
       <c r="H1997" t="n">
-        <v>4.573350833968052</v>
+        <v>4.573350833968053</v>
       </c>
     </row>
     <row r="1998">
@@ -52390,7 +52390,7 @@
         <v>4.549653718475295</v>
       </c>
       <c r="H1998" t="n">
-        <v>4.577602611380558</v>
+        <v>4.57760261138056</v>
       </c>
     </row>
     <row r="1999">
@@ -52416,7 +52416,7 @@
         <v>4.570420243256017</v>
       </c>
       <c r="H1999" t="n">
-        <v>4.599202664010943</v>
+        <v>4.599202664010945</v>
       </c>
     </row>
     <row r="2000">
@@ -52442,7 +52442,7 @@
         <v>4.62577358646665</v>
       </c>
       <c r="H2000" t="n">
-        <v>4.655002978239772</v>
+        <v>4.655002978239774</v>
       </c>
     </row>
     <row r="2001">
@@ -52468,7 +52468,7 @@
         <v>4.619969100283137</v>
       </c>
       <c r="H2001" t="n">
-        <v>4.650269105813518</v>
+        <v>4.650269105813519</v>
       </c>
     </row>
     <row r="2002">
@@ -52494,7 +52494,7 @@
         <v>4.709657411726367</v>
       </c>
       <c r="H2002" t="n">
-        <v>4.74121129343317</v>
+        <v>4.741211293433172</v>
       </c>
     </row>
     <row r="2003">
@@ -52520,7 +52520,7 @@
         <v>4.738890666176031</v>
       </c>
       <c r="H2003" t="n">
-        <v>4.772825852313336</v>
+        <v>4.772825852313338</v>
       </c>
     </row>
     <row r="2004">
@@ -52546,7 +52546,7 @@
         <v>4.711518094985482</v>
       </c>
       <c r="H2004" t="n">
-        <v>4.746300214521558</v>
+        <v>4.74630021452156</v>
       </c>
     </row>
     <row r="2005">
@@ -52572,7 +52572,7 @@
         <v>4.733280810519846</v>
       </c>
       <c r="H2005" t="n">
-        <v>4.769007233533292</v>
+        <v>4.769007233533293</v>
       </c>
     </row>
     <row r="2006">
@@ -52598,7 +52598,7 @@
         <v>4.748181345578626</v>
       </c>
       <c r="H2006" t="n">
-        <v>4.783946217931664</v>
+        <v>4.783946217931666</v>
       </c>
     </row>
     <row r="2007">
@@ -52624,7 +52624,7 @@
         <v>4.743008891212256</v>
       </c>
       <c r="H2007" t="n">
-        <v>4.780072843167562</v>
+        <v>4.780072843167564</v>
       </c>
     </row>
     <row r="2008">
@@ -52650,7 +52650,7 @@
         <v>4.752873070534473</v>
       </c>
       <c r="H2008" t="n">
-        <v>4.788363763223687</v>
+        <v>4.788363763223689</v>
       </c>
     </row>
     <row r="2009">
@@ -52676,7 +52676,7 @@
         <v>4.787590871572712</v>
       </c>
       <c r="H2009" t="n">
-        <v>4.820885614756707</v>
+        <v>4.820885614756709</v>
       </c>
     </row>
     <row r="2010">
@@ -52702,7 +52702,7 @@
         <v>4.77063385005245</v>
       </c>
       <c r="H2010" t="n">
-        <v>4.804471521702667</v>
+        <v>4.804471521702669</v>
       </c>
     </row>
     <row r="2011">
@@ -52728,7 +52728,7 @@
         <v>4.773175769200533</v>
       </c>
       <c r="H2011" t="n">
-        <v>4.806840355271208</v>
+        <v>4.80684035527121</v>
       </c>
     </row>
     <row r="2012">
@@ -52754,7 +52754,7 @@
         <v>4.758663948193901</v>
       </c>
       <c r="H2012" t="n">
-        <v>4.792188757139424</v>
+        <v>4.792188757139426</v>
       </c>
     </row>
     <row r="2013">
@@ -52780,7 +52780,7 @@
         <v>4.739275894945761</v>
       </c>
       <c r="H2013" t="n">
-        <v>4.772222344919681</v>
+        <v>4.772222344919682</v>
       </c>
     </row>
     <row r="2014">
@@ -52806,7 +52806,7 @@
         <v>4.735034029434839</v>
       </c>
       <c r="H2014" t="n">
-        <v>4.767198168208596</v>
+        <v>4.767198168208598</v>
       </c>
     </row>
     <row r="2015">
@@ -52832,7 +52832,7 @@
         <v>4.722166623737641</v>
       </c>
       <c r="H2015" t="n">
-        <v>4.753245866071116</v>
+        <v>4.753245866071118</v>
       </c>
     </row>
     <row r="2016">
@@ -52858,7 +52858,7 @@
         <v>4.740751166248381</v>
       </c>
       <c r="H2016" t="n">
-        <v>4.771566724904264</v>
+        <v>4.771566724904265</v>
       </c>
     </row>
     <row r="2017">
@@ -52884,7 +52884,7 @@
         <v>4.728529114774416</v>
       </c>
       <c r="H2017" t="n">
-        <v>4.759422651282025</v>
+        <v>4.759422651282027</v>
       </c>
     </row>
     <row r="2018">
@@ -52910,7 +52910,7 @@
         <v>4.715858502603301</v>
       </c>
       <c r="H2018" t="n">
-        <v>4.748261875647693</v>
+        <v>4.748261875647695</v>
       </c>
     </row>
     <row r="2019">
@@ -52936,7 +52936,7 @@
         <v>4.720006851617955</v>
       </c>
       <c r="H2019" t="n">
-        <v>4.751537347558574</v>
+        <v>4.751537347558576</v>
       </c>
     </row>
     <row r="2020">
@@ -52962,7 +52962,7 @@
         <v>4.730173932334026</v>
       </c>
       <c r="H2020" t="n">
-        <v>4.760808751208667</v>
+        <v>4.760808751208669</v>
       </c>
     </row>
     <row r="2021">
@@ -52988,7 +52988,7 @@
         <v>4.730344051570679</v>
       </c>
       <c r="H2021" t="n">
-        <v>4.758919417077068</v>
+        <v>4.758919417077069</v>
       </c>
     </row>
     <row r="2022">
@@ -53014,7 +53014,7 @@
         <v>4.720313786448492</v>
       </c>
       <c r="H2022" t="n">
-        <v>4.744767580793113</v>
+        <v>4.744767580793114</v>
       </c>
     </row>
   </sheetData>
